--- a/liaisons_Super_Constellation/Reseau_Flying_Tiger_L1049H_sourced.xlsx
+++ b/liaisons_Super_Constellation/Reseau_Flying_Tiger_L1049H_sourced.xlsx
@@ -578,30 +578,210 @@
       <c r="A6" t="str">
         <v/>
       </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+      <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Notes techniques &amp; historiques :</v>
+        <v>Notes :</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>Sources : Flying Tiger Line reçoit dix L-1049H (convertibles cargo/passagers) en 1957 ; exploités sur le fret nord-américain et pour le Military Air Transport Service (MATS). Le vol 739 fut une charte MATS Travis AFB → Saïgon.</v>
       </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+      <c r="C8" t="str">
+        <v/>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>[S] Sourcé : L-1049H convertible ; réseau fret domestique + chartes militaires transpacifiques (MATS).</v>
       </c>
+      <c r="B9" t="str">
+        <v/>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v>[R] Reconstitué : numéros/contrats et horaires exacts.</v>
       </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v>* Arrivée le lendemain (+1 jour). [**] Passage de la ligne de changement de date. [***] Arrivée à J+2. [Tech] = escale technique.</v>
+      </c>
+      <c r="B11" t="str">
+        <v/>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
